--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov_Krish.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov_Krish.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akl0407\Desktop\Academia\GitHub\STAT390_LegalAid_Fall2025\Clarifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF48CFA-3657-4300-9CDE-578A187BB501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C694E4-B35C-4FA2-803E-2A6301BFCC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="627" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="627" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
   <sheets>
     <sheet name="termination reason" sheetId="4" r:id="rId1"/>
@@ -1033,7 +1033,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1093,9 +1093,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -1772,7 +1769,7 @@
       <c r="D9" s="3">
         <v>1.760418961408287</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="24">
         <f>C9/248442</f>
         <v>0.20098453562602137</v>
       </c>
@@ -1986,11 +1983,11 @@
       <c r="D24" s="3">
         <v>1</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="23">
         <f>248442-C24-C9</f>
         <v>186694</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="23">
         <f>C24-9158</f>
         <v>2657</v>
       </c>
@@ -2008,11 +2005,11 @@
       <c r="D25" s="3">
         <v>1.3119709794437726</v>
       </c>
-      <c r="E25" s="25">
+      <c r="E25" s="24">
         <f>E24/248442</f>
         <v>0.75145909306799974</v>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="24">
         <f>F24/248442</f>
         <v>1.0694649052897659E-2</v>
       </c>
@@ -4024,7 +4021,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7750F3-75BB-482E-9AD7-33391182A4F5}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K83"/>
   <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4"/>
   <cols>
@@ -4073,7 +4069,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="57.6" hidden="1">
+    <row r="2" spans="1:11" ht="57.6">
       <c r="A2" s="19" t="s">
         <v>37</v>
       </c>
@@ -4105,7 +4101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="28.8" hidden="1">
+    <row r="3" spans="1:11" ht="28.8">
       <c r="A3" s="19" t="s">
         <v>40</v>
       </c>
@@ -4169,7 +4165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="72" hidden="1">
+    <row r="5" spans="1:11" ht="72">
       <c r="A5" s="19" t="s">
         <v>41</v>
       </c>
@@ -4233,7 +4229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="72" hidden="1">
+    <row r="7" spans="1:11" ht="72">
       <c r="A7" s="19" t="s">
         <v>44</v>
       </c>
@@ -4333,7 +4329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="62.25" hidden="1" customHeight="1">
+    <row r="10" spans="1:11" ht="62.25" customHeight="1">
       <c r="A10" s="19" t="s">
         <v>58</v>
       </c>
@@ -4365,7 +4361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="72" hidden="1">
+    <row r="11" spans="1:11" ht="72">
       <c r="A11" s="19" t="s">
         <v>56</v>
       </c>
@@ -4397,7 +4393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="22" customFormat="1" ht="50.25" hidden="1" customHeight="1">
+    <row r="12" spans="1:11" s="22" customFormat="1" ht="50.25" customHeight="1">
       <c r="A12" s="19" t="s">
         <v>65</v>
       </c>
@@ -4431,7 +4427,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1">
+    <row r="13" spans="1:11">
       <c r="A13" s="19" t="s">
         <v>43</v>
       </c>
@@ -4463,7 +4459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1">
+    <row r="14" spans="1:11">
       <c r="A14" s="19" t="s">
         <v>68</v>
       </c>
@@ -4529,7 +4525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="28.8" hidden="1">
+    <row r="16" spans="1:11" ht="28.8">
       <c r="A16" s="19" t="s">
         <v>72</v>
       </c>
@@ -4559,7 +4555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1">
+    <row r="17" spans="1:11">
       <c r="A17" s="19" t="s">
         <v>76</v>
       </c>
@@ -4625,7 +4621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1">
+    <row r="19" spans="1:11">
       <c r="A19" s="19" t="s">
         <v>79</v>
       </c>
@@ -4657,7 +4653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1">
+    <row r="20" spans="1:11">
       <c r="A20" s="19" t="s">
         <v>54</v>
       </c>
@@ -4817,7 +4813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1">
+    <row r="25" spans="1:11">
       <c r="A25" s="19" t="s">
         <v>71</v>
       </c>
@@ -4881,7 +4877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1">
+    <row r="27" spans="1:11">
       <c r="A27" s="19" t="s">
         <v>100</v>
       </c>
@@ -4977,7 +4973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="72" hidden="1">
+    <row r="30" spans="1:11" ht="72">
       <c r="A30" s="19" t="s">
         <v>102</v>
       </c>
@@ -5007,7 +5003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="28.8" hidden="1">
+    <row r="31" spans="1:11" ht="28.8">
       <c r="A31" s="19" t="s">
         <v>74</v>
       </c>
@@ -5039,7 +5035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1">
+    <row r="32" spans="1:11">
       <c r="A32" s="19" t="s">
         <v>47</v>
       </c>
@@ -5103,7 +5099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1">
+    <row r="34" spans="1:11">
       <c r="A34" s="19" t="s">
         <v>110</v>
       </c>
@@ -5113,7 +5109,7 @@
       <c r="C34" s="9">
         <v>541</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="10">
         <f t="shared" si="0"/>
         <v>2.1775706201044914E-3</v>
       </c>
@@ -5137,7 +5133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1">
+    <row r="35" spans="1:11">
       <c r="A35" s="19" t="s">
         <v>80</v>
       </c>
@@ -5233,7 +5229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1">
+    <row r="38" spans="1:11">
       <c r="A38" s="19" t="s">
         <v>83</v>
       </c>
@@ -5265,7 +5261,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1">
+    <row r="39" spans="1:11">
       <c r="A39" s="19" t="s">
         <v>81</v>
       </c>
@@ -5361,7 +5357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="57.6" hidden="1">
+    <row r="42" spans="1:11" ht="57.6">
       <c r="A42" s="19" t="s">
         <v>116</v>
       </c>
@@ -5391,7 +5387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1">
+    <row r="43" spans="1:11">
       <c r="A43" s="19" t="s">
         <v>77</v>
       </c>
@@ -5489,7 +5485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="28.8" hidden="1">
+    <row r="46" spans="1:11" ht="28.8">
       <c r="A46" s="19" t="s">
         <v>105</v>
       </c>
@@ -5589,7 +5585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1">
+    <row r="49" spans="1:11">
       <c r="A49" s="19" t="s">
         <v>124</v>
       </c>
@@ -5679,7 +5675,7 @@
       <c r="J51" s="19"/>
       <c r="K51" s="19"/>
     </row>
-    <row r="52" spans="1:11" ht="28.8" hidden="1">
+    <row r="52" spans="1:11" ht="28.8">
       <c r="A52" s="19" t="s">
         <v>128</v>
       </c>
@@ -5713,7 +5709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1">
+    <row r="53" spans="1:11">
       <c r="A53" s="19" t="s">
         <v>132</v>
       </c>
@@ -5777,7 +5773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1">
+    <row r="55" spans="1:11">
       <c r="A55" s="19" t="s">
         <v>89</v>
       </c>
@@ -5809,7 +5805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1">
+    <row r="56" spans="1:11">
       <c r="A56" s="19" t="s">
         <v>96</v>
       </c>
@@ -5841,7 +5837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1">
+    <row r="57" spans="1:11">
       <c r="A57" s="19" t="s">
         <v>78</v>
       </c>
@@ -5873,7 +5869,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="72" hidden="1">
+    <row r="58" spans="1:11" ht="72">
       <c r="A58" s="5" t="s">
         <v>142</v>
       </c>
@@ -5907,7 +5903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="28.8" hidden="1">
+    <row r="59" spans="1:11" ht="28.8">
       <c r="A59" s="19" t="s">
         <v>144</v>
       </c>
@@ -5941,7 +5937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="28.8" hidden="1">
+    <row r="60" spans="1:11" ht="28.8">
       <c r="A60" s="5" t="s">
         <v>92</v>
       </c>
@@ -6037,7 +6033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1">
+    <row r="63" spans="1:11">
       <c r="A63" s="5" t="s">
         <v>57</v>
       </c>
@@ -6067,7 +6063,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1">
+    <row r="64" spans="1:11">
       <c r="A64" s="19" t="s">
         <v>126</v>
       </c>
@@ -6099,7 +6095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="57.6" hidden="1">
+    <row r="65" spans="1:11" ht="57.6">
       <c r="A65" s="5" t="s">
         <v>98</v>
       </c>
@@ -6131,7 +6127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="72" hidden="1">
+    <row r="66" spans="1:11" ht="72">
       <c r="A66" s="5" t="s">
         <v>59</v>
       </c>
@@ -6197,7 +6193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="72" hidden="1">
+    <row r="68" spans="1:11" ht="72">
       <c r="A68" s="5" t="s">
         <v>87</v>
       </c>
@@ -6229,7 +6225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="57.6" hidden="1">
+    <row r="69" spans="1:11" ht="57.6">
       <c r="A69" s="5" t="s">
         <v>86</v>
       </c>
@@ -6361,7 +6357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="57.6" hidden="1">
+    <row r="73" spans="1:11" ht="57.6">
       <c r="A73" s="5" t="s">
         <v>129</v>
       </c>
@@ -6427,7 +6423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="57.6" hidden="1">
+    <row r="75" spans="1:11" ht="57.6">
       <c r="A75" s="5" t="s">
         <v>85</v>
       </c>
@@ -6493,7 +6489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="57.6" hidden="1">
+    <row r="77" spans="1:11" ht="57.6">
       <c r="A77" s="5" t="s">
         <v>148</v>
       </c>
@@ -6593,7 +6589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="86.4" hidden="1">
+    <row r="80" spans="1:11" ht="86.4">
       <c r="A80" s="5" t="s">
         <v>61</v>
       </c>
@@ -6693,7 +6689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="57.6" hidden="1">
+    <row r="83" spans="1:11" ht="57.6">
       <c r="A83" s="5" t="s">
         <v>153</v>
       </c>
@@ -6726,14 +6722,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K83" xr:uid="{4A7750F3-75BB-482E-9AD7-33391182A4F5}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="Abandoned"/>
-        <filter val="Abandoned (tenative)"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K83" xr:uid="{4A7750F3-75BB-482E-9AD7-33391182A4F5}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov_Krish.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov_Krish.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akl0407\Desktop\Academia\GitHub\STAT390_LegalAid_Fall2025\Clarifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C694E4-B35C-4FA2-803E-2A6301BFCC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B466B642-3FDF-46F5-A2DF-35133624F723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="627" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="627" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
   <sheets>
     <sheet name="termination reason" sheetId="4" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="305">
   <si>
     <t>Termination Reason</t>
   </si>
@@ -677,9 +677,6 @@
     <t>Main Menu, Holiday &amp; Closed Menu</t>
   </si>
   <si>
-    <t>Positive (Tentative)</t>
-  </si>
-  <si>
     <t>Yes</t>
   </si>
   <si>
@@ -701,237 +698,277 @@
     <t>Positive / Negative / Neutral</t>
   </si>
   <si>
+    <t>Main Menu</t>
+  </si>
+  <si>
+    <t>Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu</t>
+  </si>
+  <si>
+    <t>Neutral / Negative</t>
+  </si>
+  <si>
+    <t>Legal Menu</t>
+  </si>
+  <si>
+    <t>Farmworker Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Based on info from Mark, this reflects no activity at Farmworker Menu and cannot progress without a selection; either call disconnects after max number of repetitions or the caller hangs up; max step counter is unknown so believe calls should be considered abandoned </t>
+  </si>
+  <si>
+    <t>N/A - Ad Hoc Outbound Call</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>No input for language selection;</t>
+  </si>
+  <si>
+    <t>Holiday &amp; Closed Menu</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Appointment Menu</t>
+  </si>
+  <si>
+    <t>Caller has an appointment scheduled</t>
+  </si>
+  <si>
+    <t>Other Legal Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive </t>
+  </si>
+  <si>
+    <t>Caller requests an interpreter</t>
+  </si>
+  <si>
+    <t>Housing menu</t>
+  </si>
+  <si>
+    <t>Family menu</t>
+  </si>
+  <si>
+    <t>Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal Menu </t>
+  </si>
+  <si>
+    <t>Pre-legal seniors menu</t>
+  </si>
+  <si>
+    <t>HIV Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Menu </t>
+  </si>
+  <si>
+    <t>Caller listens to message; no option given to return to previous menus</t>
+  </si>
+  <si>
+    <t>No input</t>
+  </si>
+  <si>
+    <t>Immigration menu</t>
+  </si>
+  <si>
+    <t>Pre-Legal Seniors Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abandoned </t>
+  </si>
+  <si>
+    <t>Family Menu</t>
+  </si>
+  <si>
+    <t>Based on verbiage, unsure of what selection at Family Menu leads to this action, always then transferred to CBT Agent (thus assumed to be a positive outcome)</t>
+  </si>
+  <si>
+    <t>Benefits Menu</t>
+  </si>
+  <si>
+    <t>Callers outside Cook County or calling on someone else's behalf  (without POA) should abandon</t>
+  </si>
+  <si>
+    <t>Caller is non-Cook County Senior and did not make a selection after message</t>
+  </si>
+  <si>
+    <t>Employment menu</t>
+  </si>
+  <si>
+    <t>No activity</t>
+  </si>
+  <si>
+    <t>Caller selected Other Legal option (8) in Suburban Seniors Menu</t>
+  </si>
+  <si>
+    <t>Immigration Menu</t>
+  </si>
+  <si>
+    <t>No Agent Name for attempted courtesy callback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assuming this corresponds to Farm Worker Voicemail transfer on flow charts </t>
+  </si>
+  <si>
+    <t>Verbiage tells callers that they can leave comments online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu, </t>
+  </si>
+  <si>
+    <t>Outbound call failed to connect; system error</t>
+  </si>
+  <si>
+    <t>Employment Menu</t>
+  </si>
+  <si>
+    <t>Pre-Legal Seniors</t>
+  </si>
+  <si>
+    <t>Should check if agents are logged into queue; if last activity, call never entered queue -&gt; system error, customer may end call after waiting (not considering it abandonment)</t>
+  </si>
+  <si>
+    <t>System failure in courtesy callback attempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caller hangs up before being connected with an agent, system tries to progress but gives error since there's no caller </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-Legal Seniors </t>
+  </si>
+  <si>
+    <t>Caller did not finish confirming callback</t>
+  </si>
+  <si>
+    <t>customer made it to a queue but was never connected with an agent or scheduled a callback. Likely that customer abandoned the call after waiting.</t>
+  </si>
+  <si>
+    <t>Should check if agents are logged into queue, if last activity then caller never entered the queue (never heard pre-queue message1), customer may have ended call after waiting</t>
+  </si>
+  <si>
+    <t>VIvi</t>
+  </si>
+  <si>
+    <t>Pre-Legal Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queues Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-Legal Menu </t>
+  </si>
+  <si>
+    <t>LAC does not serve</t>
+  </si>
+  <si>
+    <t>Staff directory</t>
+  </si>
+  <si>
     <t>If EP name = 'Closed Queue Menu Telephony EP', then Negative, and type = "Closed queue",
-otherwise Positive, type = 'Reached voicemail', if EP name = 'Closed Hours-Holidays Menu Telephony EP' then neutral, and type = 'After hours call</t>
-  </si>
-  <si>
-    <t>Main Menu</t>
-  </si>
-  <si>
-    <t>Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu</t>
-  </si>
-  <si>
-    <t>Neutral / Negative</t>
-  </si>
-  <si>
-    <t>If EP name = Closed Hours-Holidays Menu Telephony EP	, then Neutral, type = "After hours call"
-If EP name = Closed Queue Menu Telephony EP, then Negative, type = "Closed Queue"</t>
-  </si>
-  <si>
-    <t>Legal Menu</t>
-  </si>
-  <si>
-    <t>Farmworker Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negative </t>
-  </si>
-  <si>
-    <t>Abandoned (tenative)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Based on info from Mark, this reflects no activity at Farmworker Menu and cannot progress without a selection; either call disconnects after max number of repetitions or the caller hangs up; max step counter is unknown so believe calls should be considered abandoned </t>
-  </si>
-  <si>
-    <t>N/A - Ad Hoc Outbound Call</t>
-  </si>
-  <si>
-    <t>Based on info from Mark, system sets caller ID for outbound call, but there is no activity suggesting the call is picked up, these calls are not to customers so should not be included in analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu</t>
-  </si>
-  <si>
-    <t>If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect  to customer; uncertainty b/c there are not activity names that indicate connection in the data</t>
-  </si>
-  <si>
-    <t>Positive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Front Desk </t>
-  </si>
-  <si>
-    <t>No input for language selection;</t>
-  </si>
-  <si>
-    <t>Holiday &amp; Closed Menu</t>
-  </si>
-  <si>
-    <t>Neutral</t>
-  </si>
-  <si>
-    <t>Closed</t>
-  </si>
-  <si>
-    <t>Appointment Menu</t>
-  </si>
-  <si>
-    <t>Caller has an appointment scheduled</t>
-  </si>
-  <si>
-    <t>Other Legal Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive </t>
-  </si>
-  <si>
-    <t>Caller requests an interpreter</t>
-  </si>
-  <si>
-    <t>Housing menu</t>
-  </si>
-  <si>
-    <t>Voicemail Transfer</t>
-  </si>
-  <si>
-    <t>Family menu</t>
-  </si>
-  <si>
-    <t>Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legal Menu </t>
-  </si>
-  <si>
-    <t>Pre-legal seniors menu</t>
-  </si>
-  <si>
-    <t>HIV Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive / Neutral (tenative) </t>
-  </si>
-  <si>
-    <t>If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect; uncertainty b/c there are not activity names that indicate connection in the data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Menu </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive (tenative) </t>
-  </si>
-  <si>
-    <t>Caller listens to message; no option given to return to previous menus</t>
-  </si>
-  <si>
-    <t>Issue not handled by LAC</t>
-  </si>
-  <si>
-    <t>No input</t>
-  </si>
-  <si>
-    <t>Immigration menu</t>
-  </si>
-  <si>
-    <t>Pre-Legal Seniors Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abandoned </t>
-  </si>
-  <si>
-    <t>Family Menu</t>
-  </si>
-  <si>
-    <t>Positive (tentative)</t>
-  </si>
-  <si>
-    <t>Based on verbiage, unsure of what selection at Family Menu leads to this action, always then transferred to CBT Agent (thus assumed to be a positive outcome)</t>
-  </si>
-  <si>
-    <t>Benefits Menu</t>
-  </si>
-  <si>
-    <t>Callers outside Cook County or calling on someone else's behalf  (without POA) should abandon</t>
-  </si>
-  <si>
-    <t>Caller is non-Cook County Senior and did not make a selection after message</t>
-  </si>
-  <si>
-    <t>Employment menu</t>
-  </si>
-  <si>
-    <t>No activity</t>
-  </si>
-  <si>
-    <t>Caller selected Other Legal option (8) in Suburban Seniors Menu</t>
-  </si>
-  <si>
-    <t>Immigration Menu</t>
-  </si>
-  <si>
-    <t>Voice Mail Transfer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closed </t>
-  </si>
-  <si>
-    <t>Unsuccessful Courtesy Callback</t>
-  </si>
-  <si>
-    <t>No Agent Name for attempted courtesy callback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assuming this corresponds to Farm Worker Voicemail transfer on flow charts </t>
-  </si>
-  <si>
-    <t>Verbiage tells callers that they can leave comments online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu, </t>
-  </si>
-  <si>
-    <t>Outbound call failed to connect; system error</t>
-  </si>
-  <si>
-    <t>Employment Menu</t>
-  </si>
-  <si>
-    <t>Pre-Legal Seniors</t>
-  </si>
-  <si>
-    <t>Should check if agents are logged into queue; if last activity, call never entered queue -&gt; system error, customer may end call after waiting (not considering it abandonment)</t>
-  </si>
-  <si>
-    <t>System failure in courtesy callback attempt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caller hangs up before being connected with an agent, system tries to progress but gives error since there's no caller </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-Legal Seniors </t>
-  </si>
-  <si>
-    <t>Caller did not finish confirming callback</t>
-  </si>
-  <si>
-    <t>customer made it to a queue but was never connected with an agent or scheduled a callback. Likely that customer abandoned the call after waiting.</t>
-  </si>
-  <si>
-    <t>Should check if agents are logged into queue, if last activity then caller never entered the queue (never heard pre-queue message1), customer may have ended call after waiting</t>
-  </si>
-  <si>
-    <t>VIvi</t>
-  </si>
-  <si>
-    <t>Pre-Legal Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queues Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Play Courtesy CallBack Confirmation" . This is typically played right before the contact is disconnected from the system. The consumer selected a courtesy callback but hung up before the system could disconnect so this is neutral. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-Legal Menu </t>
-  </si>
-  <si>
-    <t>No language selected</t>
-  </si>
-  <si>
-    <t>LAC does not serve</t>
+if EP name = 'Closed Hours-Holidays Menu Telephony EP' then neutral, and type = 'Closed hours, otherwise Positive, type = 'Clinic Voicemail'</t>
+  </si>
+  <si>
+    <t>multiple (check comment)</t>
+  </si>
+  <si>
+    <t>Krish comment (1 Dec): As all occurences are accompanied by an Agent name, and call duration for 99% of calls is at least 20 seconds, assume that the call is answered by an agent in this case, and outcome is Positive
+Student comment:
+If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect  to customer; uncertainty b/c there are not activity names that indicate connection in the data</t>
+  </si>
+  <si>
+    <t>No language selected (FD1)</t>
+  </si>
+  <si>
+    <t>Appt / feedback</t>
+  </si>
+  <si>
+    <t>Connected to agent</t>
+  </si>
+  <si>
+    <t>Krish comment (1Dec): It is ok, this outcome will be examined under caller type as intake outdial. Keep these calls in the analysis.
+Student comment: Based on info from Mark, system sets caller ID for outbound call, but there is no activity suggesting the call is picked up, these calls are not to customers so should not be included in analysis</t>
+  </si>
+  <si>
+    <t>Negative / Neutral</t>
+  </si>
+  <si>
+    <t>If the caller has been to ['OtherLegalPersonalInjuryMenu','OtherLegalCriminalCaseMenu', or                                                       'OtherLegalOtherMenu','ClinicVoicemailTransfer' earlier, classify the calls as Neutral, type = "LAC does not serve". If the call has not been inside this menu, then Negative, and type = "Abandoned"</t>
+  </si>
+  <si>
+    <t>Interpreter needed (FD, Legal menu)</t>
+  </si>
+  <si>
+    <t>Criminal Voicemail</t>
+  </si>
+  <si>
+    <t>HIV Voicemail</t>
+  </si>
+  <si>
+    <t>Krish comment (1 Dec): As all occurences are accompanied by an Agent name, and call duration for 99% of calls is at least 20 seconds, assume that the call is answered by an agent in this case, and outcome is Positive
+Student comment:
+If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect; uncertainty b/c there are not activity names that indicate connection in the data</t>
+  </si>
+  <si>
+    <t>Address Voicemail</t>
+  </si>
+  <si>
+    <t>No selection on Main menu (FD3)</t>
+  </si>
+  <si>
+    <t>Chatbot experiment (Family menu)</t>
+  </si>
+  <si>
+    <t>Veterans Voicemail</t>
+  </si>
+  <si>
+    <t>This is when the caller does not have anything under Activity Name</t>
+  </si>
+  <si>
+    <t>Trafficking Voicemail</t>
+  </si>
+  <si>
+    <t>Closed hours</t>
+  </si>
+  <si>
+    <t>Farmworker Voicemail</t>
+  </si>
+  <si>
+    <t>Feedback</t>
+  </si>
+  <si>
+    <t>If EP name = Closed Hours-Holidays Menu Telephony EP	, then Neutral, type = "Closed hours"
+If EP name = Closed Queue Menu Telephony EP, then Negative, type = "Closed Queue"
+If EP Name = Pre-Legal Menu Seniors Menu Telephony EP, then Neutral, type = "LAC does not serve"
+If EP Name = Courtesy Callback Telephony EP, then Negative, type = "Failed courtsey callback"</t>
+  </si>
+  <si>
+    <t>Failed courtsey callback</t>
+  </si>
+  <si>
+    <t>Outbound call failed</t>
+  </si>
+  <si>
+    <t>Krish comment (1Dec): This always happens in a queue, hence abandoned
+Student comment:
+Should check if agents are logged into queue; if last activity, call never entered queue -&gt; system error, customer may end call after waiting (not considering it abandonment)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krish (1Dec): But the caller was not called back, leading to a failed callback, a negative outcome
+"Play Courtesy CallBack Confirmation" . This is typically played right before the contact is disconnected from the system. The consumer selected a courtesy callback but hung up before the system could disconnect so this is neutral. </t>
   </si>
 </sst>
 </file>
@@ -978,18 +1015,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1033,7 +1064,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1045,9 +1076,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1065,36 +1093,36 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1432,10 +1460,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981D87C8-B39B-4C38-8BFC-6165BBCFDE55}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.83984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1662,17 +1690,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD07D810-8110-4FD1-8A65-1F5B70F5B858}">
   <dimension ref="A3:F167"/>
-  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.83984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.15625" customWidth="1"/>
-    <col min="4" max="4" width="9.15625" customWidth="1"/>
-    <col min="5" max="5" width="11.68359375" customWidth="1"/>
-    <col min="6" max="6" width="31.41796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.26171875" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" s="5" customFormat="1" ht="28.8">
+    <row r="3" spans="1:5" s="5" customFormat="1" ht="30">
       <c r="A3" s="4" t="s">
         <v>28</v>
       </c>
@@ -1769,7 +1797,7 @@
       <c r="D9" s="3">
         <v>1.760418961408287</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="17">
         <f>C9/248442</f>
         <v>0.20098453562602137</v>
       </c>
@@ -1983,11 +2011,11 @@
       <c r="D24" s="3">
         <v>1</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="16">
         <f>248442-C24-C9</f>
         <v>186694</v>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="16">
         <f>C24-9158</f>
         <v>2657</v>
       </c>
@@ -2005,11 +2033,11 @@
       <c r="D25" s="3">
         <v>1.3119709794437726</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="17">
         <f>E24/248442</f>
         <v>0.75145909306799974</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="17">
         <f>F24/248442</f>
         <v>1.0694649052897659E-2</v>
       </c>
@@ -4022,19 +4050,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7750F3-75BB-482E-9AD7-33391182A4F5}">
   <dimension ref="A1:K83"/>
-  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.41796875" customWidth="1"/>
-    <col min="2" max="2" width="22.26171875" customWidth="1"/>
-    <col min="3" max="3" width="17.15625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.15625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="28.41796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.26171875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.26171875" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="43.2">
+    <row r="1" spans="1:11" ht="45">
       <c r="A1" s="6" t="s">
         <v>196</v>
       </c>
@@ -4069,17 +4097,17 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="57.6">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:11" ht="75">
+      <c r="A2" s="15" t="s">
         <v>37</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="8">
         <v>39892</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <f>C2/SUM(($C$2:$C$83))</f>
         <v>0.16056866391350899</v>
       </c>
@@ -4101,49 +4129,49 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="28.8">
-      <c r="A3" s="19" t="s">
+    <row r="3" spans="1:11" ht="30">
+      <c r="A3" s="15" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>28035</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <f t="shared" ref="D3:D66" si="0">C3/SUM(($C$2:$C$83))</f>
         <v>0.11284323906585843</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5" t="s">
-        <v>212</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5" t="s">
         <v>209</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K3" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="28.8">
-      <c r="A4" s="19" t="s">
+    <row r="4" spans="1:11" ht="30">
+      <c r="A4" s="15" t="s">
         <v>32</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C4" s="9">
+        <v>213</v>
+      </c>
+      <c r="C4" s="8">
         <v>27545</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <f t="shared" si="0"/>
         <v>0.11087094774635528</v>
       </c>
@@ -4151,7 +4179,7 @@
         <v>207</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
@@ -4159,55 +4187,57 @@
         <v>209</v>
       </c>
       <c r="J4" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="105">
+      <c r="A5" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="72">
-      <c r="A5" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>25721</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <f t="shared" si="0"/>
         <v>0.10352919393661297</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="F5" s="5"/>
+        <v>217</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>279</v>
+      </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>219</v>
+        <v>278</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>209</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K5" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="15" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C6" s="9">
+        <v>218</v>
+      </c>
+      <c r="C6" s="8">
         <v>13075</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <f t="shared" si="0"/>
         <v>5.2627977556129801E-2</v>
       </c>
@@ -4215,7 +4245,7 @@
         <v>207</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -4223,55 +4253,57 @@
         <v>209</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K6" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="72">
-      <c r="A7" s="19" t="s">
+    <row r="7" spans="1:11" ht="165">
+      <c r="A7" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" s="9">
+      <c r="B7" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" s="8">
         <v>12010</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <f t="shared" si="0"/>
         <v>4.8341262749454599E-2</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="F7" s="5"/>
+        <v>220</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>279</v>
+      </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>223</v>
+        <v>300</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>209</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K7" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="15" t="s">
         <v>36</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C8" s="9">
+        <v>221</v>
+      </c>
+      <c r="C8" s="8">
         <v>11987</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <f t="shared" si="0"/>
         <v>4.8248685809967717E-2</v>
       </c>
@@ -4279,7 +4311,7 @@
         <v>207</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
@@ -4287,319 +4319,327 @@
         <v>209</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K8" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="86.4">
-      <c r="A9" s="19" t="s">
+    <row r="9" spans="1:11" ht="105">
+      <c r="A9" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="C9" s="11">
+        <v>222</v>
+      </c>
+      <c r="C9" s="10">
         <v>9640</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <f t="shared" si="0"/>
         <v>3.8801812897980216E-2</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>209</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K9" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="62.25" customHeight="1">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="15" t="s">
         <v>58</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="C10" s="11">
+        <v>225</v>
+      </c>
+      <c r="C10" s="10">
         <v>9358</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f t="shared" si="0"/>
         <v>3.7666739118184529E-2</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="F10" s="5"/>
+        <v>227</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>283</v>
+      </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>230</v>
+        <v>284</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K10" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="72">
-      <c r="A11" s="19" t="s">
+    <row r="11" spans="1:11" ht="210">
+      <c r="A11" s="15" t="s">
         <v>56</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="C11" s="11">
+        <v>226</v>
+      </c>
+      <c r="C11" s="10">
         <v>8939</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <f t="shared" si="0"/>
         <v>3.5980228785793066E-2</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="F11" s="5"/>
+        <v>227</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>283</v>
+      </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>232</v>
+        <v>280</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K11" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="22" customFormat="1" ht="50.25" customHeight="1">
-      <c r="A12" s="19" t="s">
+    <row r="12" spans="1:11" s="19" customFormat="1" ht="50.25" customHeight="1">
+      <c r="A12" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="C12" s="20">
+      <c r="B12" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C12" s="10">
         <v>7890</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="11">
         <f t="shared" si="0"/>
         <v>3.1757915328326128E-2</v>
       </c>
-      <c r="E12" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>294</v>
-      </c>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="K12" s="19">
+      <c r="E12" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="K12" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="15" t="s">
         <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="C13" s="9">
+        <v>229</v>
+      </c>
+      <c r="C13" s="8">
         <v>7765</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <f t="shared" si="0"/>
         <v>3.125477978763655E-2</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>238</v>
+        <v>297</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K13" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="15" t="s">
         <v>68</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C14" s="9">
+        <v>231</v>
+      </c>
+      <c r="C14" s="8">
         <v>6895</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <f t="shared" si="0"/>
         <v>2.7752956424437092E-2</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>234</v>
+        <v>282</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K14" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="19" t="s">
+    <row r="15" spans="1:11" ht="120">
+      <c r="A15" s="15" t="s">
         <v>48</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="C15" s="9">
+        <v>233</v>
+      </c>
+      <c r="C15" s="8">
         <v>6863</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <f t="shared" si="0"/>
         <v>2.7624153726020562E-2</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>207</v>
+        <v>285</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>215</v>
+        <v>279</v>
       </c>
       <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="H15" s="5" t="s">
+        <v>286</v>
+      </c>
       <c r="I15" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K15" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="28.8">
-      <c r="A16" s="19" t="s">
+    <row r="16" spans="1:11" ht="30">
+      <c r="A16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="8">
         <v>3959</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <f t="shared" si="0"/>
         <v>1.5935308844720296E-2</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="F16" s="5"/>
+        <v>227</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>277</v>
+      </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K16" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="19" t="s">
+    <row r="17" spans="1:11" ht="30">
+      <c r="A17" s="15" t="s">
         <v>76</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C17" s="9">
+        <v>221</v>
+      </c>
+      <c r="C17" s="8">
         <v>2545</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <f t="shared" si="0"/>
         <v>1.0243839608439796E-2</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>234</v>
+        <v>287</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K17" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="15" t="s">
         <v>50</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="C18" s="9">
+        <v>236</v>
+      </c>
+      <c r="C18" s="8">
         <v>2394</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="21">
         <f t="shared" si="0"/>
         <v>9.6360518752867871E-3</v>
       </c>
@@ -4607,95 +4647,95 @@
         <v>207</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K18" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="15" t="s">
         <v>79</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C19" s="9">
+        <v>221</v>
+      </c>
+      <c r="C19" s="8">
         <v>2267</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <f t="shared" si="0"/>
         <v>9.1248661659461758E-3</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>245</v>
+        <v>288</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K19" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="15" t="s">
         <v>54</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="C20" s="9">
+        <v>233</v>
+      </c>
+      <c r="C20" s="8">
         <v>2136</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <f t="shared" si="0"/>
         <v>8.5975801193034999E-3</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K20" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="15" t="s">
         <v>53</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="C21" s="9">
+        <v>237</v>
+      </c>
+      <c r="C21" s="8">
         <v>1462</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <f t="shared" si="0"/>
         <v>5.8846732839052977E-3</v>
       </c>
@@ -4703,31 +4743,31 @@
         <v>207</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K21" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="62.4">
-      <c r="A22" s="19" t="s">
+    <row r="22" spans="1:11" ht="77.25">
+      <c r="A22" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C22" s="9">
+      <c r="B22" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C22" s="8">
         <v>1287</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <f t="shared" si="0"/>
         <v>5.1802835269398892E-3</v>
       </c>
@@ -4735,31 +4775,31 @@
         <v>207</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K22" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C23" s="9">
+        <v>239</v>
+      </c>
+      <c r="C23" s="8">
         <v>1267</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="9">
         <f t="shared" si="0"/>
         <v>5.099781840429557E-3</v>
       </c>
@@ -4767,31 +4807,31 @@
         <v>207</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K23" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="15" t="s">
         <v>34</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C24" s="9">
+        <v>240</v>
+      </c>
+      <c r="C24" s="8">
         <v>1209</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="20">
         <f t="shared" si="0"/>
         <v>4.8663269495495933E-3</v>
       </c>
@@ -4799,63 +4839,63 @@
         <v>207</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K24" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="15" t="s">
         <v>71</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="C25" s="9">
+        <v>236</v>
+      </c>
+      <c r="C25" s="8">
         <v>870</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="20">
         <f t="shared" si="0"/>
         <v>3.5018233631994591E-3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
       <c r="I25" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K25" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="15" t="s">
         <v>45</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="C26" s="9">
+        <v>236</v>
+      </c>
+      <c r="C26" s="8">
         <v>837</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="20">
         <f t="shared" si="0"/>
         <v>3.3689955804574105E-3</v>
       </c>
@@ -4863,63 +4903,63 @@
         <v>207</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
       <c r="I26" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K26" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="15" t="s">
         <v>100</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="C27" s="9">
+        <v>241</v>
+      </c>
+      <c r="C27" s="8">
         <v>836</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="20">
         <f t="shared" si="0"/>
         <v>3.3649704961318939E-3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>245</v>
+        <v>289</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K27" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="62.4">
-      <c r="A28" s="19" t="s">
+    <row r="28" spans="1:11" ht="77.25">
+      <c r="A28" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C28" s="9">
+      <c r="B28" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C28" s="8">
         <v>785</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="20">
         <f t="shared" si="0"/>
         <v>3.1596911955305462E-3</v>
       </c>
@@ -4927,31 +4967,31 @@
         <v>207</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K28" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="15" t="s">
         <v>82</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="C29" s="9">
+        <v>241</v>
+      </c>
+      <c r="C29" s="8">
         <v>771</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="20">
         <f t="shared" si="0"/>
         <v>3.1033400149733138E-3</v>
       </c>
@@ -4959,125 +4999,129 @@
         <v>207</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K29" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="72">
-      <c r="A30" s="19" t="s">
+    <row r="30" spans="1:11" ht="195">
+      <c r="A30" s="15" t="s">
         <v>102</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C30" s="11">
+        <v>242</v>
+      </c>
+      <c r="C30" s="10">
         <v>694</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="22">
         <f t="shared" si="0"/>
         <v>2.793408521908534E-3</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="F30" s="5"/>
+        <v>227</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>283</v>
+      </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="28.8">
-      <c r="A31" s="19" t="s">
+    <row r="31" spans="1:11" ht="30">
+      <c r="A31" s="15" t="s">
         <v>74</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C31" s="9">
+        <v>243</v>
+      </c>
+      <c r="C31" s="8">
         <v>672</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="20">
         <f t="shared" si="0"/>
         <v>2.7048566667471682E-3</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="F31" s="5"/>
+        <v>234</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>291</v>
+      </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K31" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="15" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="C32" s="9">
+        <v>236</v>
+      </c>
+      <c r="C32" s="8">
         <v>604</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="20">
         <f t="shared" si="0"/>
         <v>2.4311509326120384E-3</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K32" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="19" t="s">
+      <c r="A33" s="15" t="s">
         <v>42</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="C33" s="9">
+        <v>237</v>
+      </c>
+      <c r="C33" s="8">
         <v>543</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="20">
         <f t="shared" si="0"/>
         <v>2.1856207887555245E-3</v>
       </c>
@@ -5085,97 +5129,97 @@
         <v>207</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K33" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="19" t="s">
+    <row r="34" spans="1:11" ht="30">
+      <c r="A34" s="15" t="s">
         <v>110</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C34" s="9">
+        <v>218</v>
+      </c>
+      <c r="C34" s="8">
         <v>541</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="20">
         <f t="shared" si="0"/>
         <v>2.1775706201044914E-3</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K34" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="15" t="s">
         <v>80</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="C35" s="9">
+        <v>237</v>
+      </c>
+      <c r="C35" s="8">
         <v>540</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="20">
         <f t="shared" si="0"/>
         <v>2.1735455357789744E-3</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K35" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="19" t="s">
+      <c r="A36" s="15" t="s">
         <v>73</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="C36" s="9">
+        <v>246</v>
+      </c>
+      <c r="C36" s="8">
         <v>527</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="20">
         <f t="shared" si="0"/>
         <v>2.1212194395472585E-3</v>
       </c>
@@ -5183,31 +5227,31 @@
         <v>207</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K36" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="19" t="s">
+      <c r="A37" s="15" t="s">
         <v>46</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C37" s="9">
+        <v>247</v>
+      </c>
+      <c r="C37" s="8">
         <v>502</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37" s="20">
         <f t="shared" si="0"/>
         <v>2.020592331409343E-3</v>
       </c>
@@ -5215,95 +5259,95 @@
         <v>207</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K37" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="15" t="s">
         <v>83</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="C38" s="9">
+        <v>233</v>
+      </c>
+      <c r="C38" s="8">
         <v>479</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="20">
         <f t="shared" si="0"/>
         <v>1.9280153919224608E-3</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K38" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="15" t="s">
         <v>81</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="9">
+        <v>233</v>
+      </c>
+      <c r="C39" s="8">
         <v>454</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D39" s="20">
         <f t="shared" si="0"/>
         <v>1.8273882837845452E-3</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K39" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="19" t="s">
+      <c r="A40" s="15" t="s">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C40" s="9">
+        <v>240</v>
+      </c>
+      <c r="C40" s="8">
         <v>444</v>
       </c>
-      <c r="D40" s="10">
+      <c r="D40" s="20">
         <f t="shared" si="0"/>
         <v>1.7871374405293791E-3</v>
       </c>
@@ -5311,31 +5355,31 @@
         <v>207</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K40" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="19" t="s">
+      <c r="A41" s="15" t="s">
         <v>64</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C41" s="9">
+        <v>240</v>
+      </c>
+      <c r="C41" s="8">
         <v>442</v>
       </c>
-      <c r="D41" s="10">
+      <c r="D41" s="20">
         <f t="shared" si="0"/>
         <v>1.779087271878346E-3</v>
       </c>
@@ -5343,93 +5387,95 @@
         <v>207</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K41" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="57.6">
-      <c r="A42" s="19" t="s">
+    <row r="42" spans="1:11" ht="60">
+      <c r="A42" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="C42" s="14">
+      <c r="B42" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="C42" s="10">
         <v>412</v>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="22">
         <f t="shared" si="0"/>
         <v>1.6583347421128473E-3</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7">
+      <c r="E42" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="F42" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="I42" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="19" t="s">
+      <c r="A43" s="15" t="s">
         <v>77</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C43" s="9">
+        <v>249</v>
+      </c>
+      <c r="C43" s="8">
         <v>353</v>
       </c>
-      <c r="D43" s="10">
+      <c r="D43" s="20">
         <f t="shared" si="0"/>
         <v>1.4208547669073666E-3</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K43" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="19" t="s">
+      <c r="A44" s="15" t="s">
         <v>66</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C44" s="9">
+        <v>251</v>
+      </c>
+      <c r="C44" s="8">
         <v>298</v>
       </c>
-      <c r="D44" s="10">
+      <c r="D44" s="20">
         <f t="shared" si="0"/>
         <v>1.1994751290039527E-3</v>
       </c>
@@ -5437,31 +5483,31 @@
         <v>207</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K44" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="28.8">
-      <c r="A45" s="19" t="s">
+    <row r="45" spans="1:11" ht="45">
+      <c r="A45" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B45" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="C45" s="16">
+      <c r="B45" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C45" s="13">
         <v>278</v>
       </c>
-      <c r="D45" s="17">
+      <c r="D45" s="23">
         <f t="shared" si="0"/>
         <v>1.1189734424936202E-3</v>
       </c>
@@ -5469,67 +5515,67 @@
         <v>207</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K45" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="28.8">
-      <c r="A46" s="19" t="s">
+    <row r="46" spans="1:11" ht="30">
+      <c r="A46" s="15" t="s">
         <v>105</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C46" s="9">
+        <v>247</v>
+      </c>
+      <c r="C46" s="8">
         <v>228</v>
       </c>
-      <c r="D46" s="10">
+      <c r="D46" s="20">
         <f t="shared" si="0"/>
         <v>9.1771922621778929E-4</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K46" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="62.4">
-      <c r="A47" s="19" t="s">
+    <row r="47" spans="1:11" ht="77.25">
+      <c r="A47" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C47" s="9">
+      <c r="B47" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C47" s="8">
         <v>219</v>
       </c>
-      <c r="D47" s="10">
+      <c r="D47" s="20">
         <f t="shared" si="0"/>
         <v>8.8149346728813973E-4</v>
       </c>
@@ -5537,33 +5583,33 @@
         <v>207</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K47" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="19" t="s">
+      <c r="A48" s="15" t="s">
         <v>38</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C48" s="9">
-        <v>212</v>
-      </c>
-      <c r="D48" s="10">
+        <v>247</v>
+      </c>
+      <c r="C48" s="8">
+        <v>212</v>
+      </c>
+      <c r="D48" s="20">
         <f t="shared" si="0"/>
         <v>8.533178770095233E-4</v>
       </c>
@@ -5571,63 +5617,63 @@
         <v>207</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K48" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="19" t="s">
+      <c r="A49" s="15" t="s">
         <v>124</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C49" s="9">
+        <v>251</v>
+      </c>
+      <c r="C49" s="8">
         <v>185</v>
       </c>
-      <c r="D49" s="10">
+      <c r="D49" s="20">
         <f t="shared" si="0"/>
         <v>7.446406002205746E-4</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>245</v>
+        <v>294</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K49" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:11">
-      <c r="A50" s="19" t="s">
+      <c r="A50" s="15" t="s">
         <v>70</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C50" s="9">
+        <v>254</v>
+      </c>
+      <c r="C50" s="8">
         <v>183</v>
       </c>
-      <c r="D50" s="10">
+      <c r="D50" s="20">
         <f t="shared" si="0"/>
         <v>7.3659043156954135E-4</v>
       </c>
@@ -5635,123 +5681,125 @@
         <v>207</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K50" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:11" s="22" customFormat="1">
-      <c r="A51" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="B51" s="19"/>
-      <c r="C51" s="20">
+    <row r="51" spans="1:11" s="19" customFormat="1" ht="30">
+      <c r="A51" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="B51" s="18"/>
+      <c r="C51" s="10">
         <v>177</v>
       </c>
-      <c r="D51" s="21">
+      <c r="D51" s="22">
         <f t="shared" si="0"/>
         <v>7.1243992561644172E-4</v>
       </c>
-      <c r="E51" s="19" t="s">
+      <c r="E51" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="F51" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="19" t="s">
+      <c r="F51" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="I51" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="J51" s="19"/>
-      <c r="K51" s="19"/>
-    </row>
-    <row r="52" spans="1:11" ht="28.8">
-      <c r="A52" s="19" t="s">
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
+    </row>
+    <row r="52" spans="1:11" ht="30">
+      <c r="A52" s="15" t="s">
         <v>128</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C52" s="9">
+        <v>247</v>
+      </c>
+      <c r="C52" s="8">
         <v>158</v>
       </c>
-      <c r="D52" s="10">
+      <c r="D52" s="20">
         <f t="shared" si="0"/>
         <v>6.3596332343162591E-4</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K52" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" s="19" t="s">
+      <c r="A53" s="15" t="s">
         <v>132</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="C53" s="9">
+        <v>257</v>
+      </c>
+      <c r="C53" s="8">
         <v>139</v>
       </c>
-      <c r="D53" s="10">
+      <c r="D53" s="20">
         <f t="shared" si="0"/>
         <v>5.594867212468101E-4</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K53" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:11">
-      <c r="A54" s="19" t="s">
+      <c r="A54" s="15" t="s">
         <v>49</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C54" s="9">
+        <v>231</v>
+      </c>
+      <c r="C54" s="8">
         <v>138</v>
       </c>
-      <c r="D54" s="10">
+      <c r="D54" s="20">
         <f t="shared" si="0"/>
         <v>5.5546163692129352E-4</v>
       </c>
@@ -5759,127 +5807,127 @@
         <v>207</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K54" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:11">
-      <c r="A55" s="19" t="s">
+      <c r="A55" s="15" t="s">
         <v>89</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C55" s="9">
+        <v>247</v>
+      </c>
+      <c r="C55" s="8">
         <v>127</v>
       </c>
-      <c r="D55" s="10">
+      <c r="D55" s="20">
         <f t="shared" si="0"/>
         <v>5.1118570934061071E-4</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K55" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:11">
-      <c r="A56" s="19" t="s">
+      <c r="A56" s="15" t="s">
         <v>96</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="C56" s="9">
+        <v>257</v>
+      </c>
+      <c r="C56" s="8">
         <v>116</v>
       </c>
-      <c r="D56" s="10">
+      <c r="D56" s="20">
         <f t="shared" si="0"/>
         <v>4.669097817599279E-4</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K56" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:11">
-      <c r="A57" s="19" t="s">
+      <c r="A57" s="15" t="s">
         <v>78</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="C57" s="9">
+        <v>229</v>
+      </c>
+      <c r="C57" s="8">
         <v>85</v>
       </c>
-      <c r="D57" s="10">
+      <c r="D57" s="20">
         <f t="shared" si="0"/>
         <v>3.4213216766891265E-4</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K57" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="72">
+    <row r="58" spans="1:11" ht="90">
       <c r="A58" s="5" t="s">
         <v>142</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="C58" s="9">
+        <v>226</v>
+      </c>
+      <c r="C58" s="8">
         <v>70</v>
       </c>
-      <c r="D58" s="10">
+      <c r="D58" s="20">
         <f t="shared" si="0"/>
         <v>2.8175590278616339E-4</v>
       </c>
@@ -5887,99 +5935,101 @@
         <v>207</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K58" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="28.8">
-      <c r="A59" s="19" t="s">
+    <row r="59" spans="1:11" ht="30">
+      <c r="A59" s="15" t="s">
         <v>144</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="C59" s="9">
+        <v>222</v>
+      </c>
+      <c r="C59" s="8">
         <v>67</v>
       </c>
-      <c r="D59" s="10">
+      <c r="D59" s="20">
         <f t="shared" si="0"/>
         <v>2.6968064980961351E-4</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>245</v>
+        <v>298</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K59" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="28.8">
+    <row r="60" spans="1:11" ht="30">
       <c r="A60" s="5" t="s">
         <v>92</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C60" s="9">
+        <v>243</v>
+      </c>
+      <c r="C60" s="8">
         <v>58</v>
       </c>
-      <c r="D60" s="10">
+      <c r="D60" s="20">
         <f t="shared" si="0"/>
         <v>2.3345489087996395E-4</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="F60" s="5"/>
+        <v>227</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>299</v>
+      </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K60" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="72">
-      <c r="A61" s="19" t="s">
+    <row r="61" spans="1:11" ht="90">
+      <c r="A61" s="15" t="s">
         <v>52</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="C61" s="9">
+        <v>261</v>
+      </c>
+      <c r="C61" s="8">
         <v>37</v>
       </c>
-      <c r="D61" s="10">
+      <c r="D61" s="20">
         <f t="shared" si="0"/>
         <v>1.4892812004411492E-4</v>
       </c>
@@ -5987,31 +6037,31 @@
         <v>207</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K61" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62" s="19" t="s">
+      <c r="A62" s="15" t="s">
         <v>51</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C62" s="9">
+        <v>243</v>
+      </c>
+      <c r="C62" s="8">
         <v>34</v>
       </c>
-      <c r="D62" s="10">
+      <c r="D62" s="20">
         <f t="shared" si="0"/>
         <v>1.3685286706756507E-4</v>
       </c>
@@ -6019,157 +6069,163 @@
         <v>207</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K62" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" ht="30">
       <c r="A63" s="5" t="s">
         <v>57</v>
       </c>
       <c r="B63" s="5"/>
-      <c r="C63" s="9">
+      <c r="C63" s="8">
         <v>32</v>
       </c>
-      <c r="D63" s="10">
+      <c r="D63" s="20">
         <f t="shared" si="0"/>
         <v>1.2880269841653182E-4</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F63" s="5"/>
+      <c r="F63" s="5" t="s">
+        <v>302</v>
+      </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K63" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:11">
-      <c r="A64" s="19" t="s">
+      <c r="A64" s="15" t="s">
         <v>126</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="C64" s="9">
+        <v>263</v>
+      </c>
+      <c r="C64" s="8">
         <v>31</v>
       </c>
-      <c r="D64" s="10">
+      <c r="D64" s="20">
         <f t="shared" si="0"/>
         <v>1.247776140910152E-4</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K64" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="57.6">
+    <row r="65" spans="1:11" ht="135">
       <c r="A65" s="5" t="s">
         <v>98</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="C65" s="9">
+        <v>264</v>
+      </c>
+      <c r="C65" s="8">
         <v>27</v>
       </c>
-      <c r="D65" s="10">
+      <c r="D65" s="20">
         <f t="shared" si="0"/>
         <v>1.0867727678894872E-4</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F65" s="5"/>
+      <c r="F65" s="5" t="s">
+        <v>214</v>
+      </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K65" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="72">
+    <row r="66" spans="1:11" ht="90">
       <c r="A66" s="5" t="s">
         <v>59</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="C66" s="9">
+        <v>261</v>
+      </c>
+      <c r="C66" s="8">
         <v>27</v>
       </c>
-      <c r="D66" s="10">
+      <c r="D66" s="20">
         <f t="shared" si="0"/>
         <v>1.0867727678894872E-4</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F66" s="5"/>
+      <c r="F66" s="5" t="s">
+        <v>301</v>
+      </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K66" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="43.2">
+    <row r="67" spans="1:11" ht="45">
       <c r="A67" s="5" t="s">
         <v>166</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C67" s="9">
+        <v>213</v>
+      </c>
+      <c r="C67" s="8">
         <v>22</v>
       </c>
-      <c r="D67" s="10">
+      <c r="D67" s="20">
         <f t="shared" ref="D67:D83" si="1">C67/SUM(($C$2:$C$83))</f>
         <v>8.855185516136563E-5</v>
       </c>
@@ -6177,33 +6233,33 @@
         <v>207</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K67" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="72">
+    <row r="68" spans="1:11" ht="90">
       <c r="A68" s="5" t="s">
         <v>87</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="C68" s="9">
+        <v>261</v>
+      </c>
+      <c r="C68" s="8">
         <v>13</v>
       </c>
-      <c r="D68" s="10">
+      <c r="D68" s="20">
         <f t="shared" si="1"/>
         <v>5.2326096231716057E-5</v>
       </c>
@@ -6211,63 +6267,65 @@
         <v>207</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
       <c r="I68" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K68" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="57.6">
+    <row r="69" spans="1:11" ht="75">
       <c r="A69" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="C69" s="9">
+        <v>268</v>
+      </c>
+      <c r="C69" s="8">
         <v>8</v>
       </c>
-      <c r="D69" s="10">
+      <c r="D69" s="20">
         <f t="shared" si="1"/>
         <v>3.2200674604132955E-5</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="F69" s="5"/>
+        <v>223</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>248</v>
+      </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K69" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="72">
+    <row r="70" spans="1:11" ht="90">
       <c r="A70" s="5" t="s">
         <v>94</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="C70" s="9">
+        <v>261</v>
+      </c>
+      <c r="C70" s="8">
         <v>5</v>
       </c>
-      <c r="D70" s="10">
+      <c r="D70" s="20">
         <f t="shared" si="1"/>
         <v>2.0125421627583099E-5</v>
       </c>
@@ -6275,33 +6333,33 @@
         <v>207</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K70" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="72">
+    <row r="71" spans="1:11" ht="90">
       <c r="A71" s="5" t="s">
         <v>95</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="C71" s="9">
+        <v>261</v>
+      </c>
+      <c r="C71" s="8">
         <v>4</v>
       </c>
-      <c r="D71" s="10">
+      <c r="D71" s="20">
         <f t="shared" si="1"/>
         <v>1.6100337302066478E-5</v>
       </c>
@@ -6309,33 +6367,33 @@
         <v>207</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K71" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:11">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="B72" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="C72" s="16">
+      <c r="B72" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C72" s="13">
         <v>4</v>
       </c>
-      <c r="D72" s="17">
+      <c r="D72" s="23">
         <f t="shared" si="1"/>
         <v>1.6100337302066478E-5</v>
       </c>
@@ -6343,63 +6401,65 @@
         <v>207</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
       <c r="I72" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K72" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="57.6">
+    <row r="73" spans="1:11" ht="75">
       <c r="A73" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C73" s="9">
+        <v>247</v>
+      </c>
+      <c r="C73" s="8">
         <v>2</v>
       </c>
-      <c r="D73" s="10">
+      <c r="D73" s="20">
         <f t="shared" si="1"/>
         <v>8.0501686510332388E-6</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F73" s="5"/>
+      <c r="F73" s="5" t="s">
+        <v>248</v>
+      </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K73" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="57.6">
+    <row r="74" spans="1:11" ht="60">
       <c r="A74" s="5" t="s">
         <v>91</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C74" s="9">
+        <v>247</v>
+      </c>
+      <c r="C74" s="8">
         <v>2</v>
       </c>
-      <c r="D74" s="10">
+      <c r="D74" s="20">
         <f t="shared" si="1"/>
         <v>8.0501686510332388E-6</v>
       </c>
@@ -6407,65 +6467,67 @@
         <v>207</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K74" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="57.6">
+    <row r="75" spans="1:11" ht="75">
       <c r="A75" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C75" s="9">
-        <v>1</v>
-      </c>
-      <c r="D75" s="10">
+        <v>239</v>
+      </c>
+      <c r="C75" s="8">
+        <v>1</v>
+      </c>
+      <c r="D75" s="20">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F75" s="5"/>
+      <c r="F75" s="5" t="s">
+        <v>214</v>
+      </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="K75" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="57.6">
+    <row r="76" spans="1:11" ht="60">
       <c r="A76" s="5" t="s">
         <v>127</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="C76" s="9">
-        <v>1</v>
-      </c>
-      <c r="D76" s="10">
+        <v>257</v>
+      </c>
+      <c r="C76" s="8">
+        <v>1</v>
+      </c>
+      <c r="D76" s="20">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
@@ -6473,65 +6535,67 @@
         <v>207</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K76" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="57.6">
+    <row r="77" spans="1:11" ht="75">
       <c r="A77" s="5" t="s">
         <v>148</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="C77" s="9">
-        <v>1</v>
-      </c>
-      <c r="D77" s="10">
+        <v>273</v>
+      </c>
+      <c r="C77" s="8">
+        <v>1</v>
+      </c>
+      <c r="D77" s="20">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F77" s="5"/>
+      <c r="F77" s="5" t="s">
+        <v>214</v>
+      </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K77" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="57.6">
+    <row r="78" spans="1:11" ht="60">
       <c r="A78" s="5" t="s">
         <v>103</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="C78" s="9">
-        <v>1</v>
-      </c>
-      <c r="D78" s="10">
+        <v>273</v>
+      </c>
+      <c r="C78" s="8">
+        <v>1</v>
+      </c>
+      <c r="D78" s="20">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
@@ -6539,99 +6603,101 @@
         <v>207</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K78" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="57.6">
+    <row r="79" spans="1:11" ht="60">
       <c r="A79" s="5" t="s">
         <v>176</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C79" s="9">
-        <v>1</v>
-      </c>
-      <c r="D79" s="10">
+        <v>249</v>
+      </c>
+      <c r="C79" s="8">
+        <v>1</v>
+      </c>
+      <c r="D79" s="20">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K79" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="86.4">
+    <row r="80" spans="1:11" ht="150">
       <c r="A80" s="5" t="s">
         <v>61</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C80" s="9">
-        <v>1</v>
-      </c>
-      <c r="D80" s="10">
+        <v>274</v>
+      </c>
+      <c r="C80" s="8">
+        <v>1</v>
+      </c>
+      <c r="D80" s="20">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F80" s="5"/>
+        <v>207</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>301</v>
+      </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K80" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="57.6">
+    <row r="81" spans="1:11" ht="60">
       <c r="A81" s="5" t="s">
         <v>115</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="C81" s="9">
-        <v>1</v>
-      </c>
-      <c r="D81" s="10">
+        <v>273</v>
+      </c>
+      <c r="C81" s="8">
+        <v>1</v>
+      </c>
+      <c r="D81" s="20">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
@@ -6639,33 +6705,33 @@
         <v>207</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K81" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="57.6">
+    <row r="82" spans="1:11" ht="60">
       <c r="A82" s="5" t="s">
         <v>112</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="C82" s="9">
-        <v>1</v>
-      </c>
-      <c r="D82" s="10">
+        <v>275</v>
+      </c>
+      <c r="C82" s="8">
+        <v>1</v>
+      </c>
+      <c r="D82" s="20">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
@@ -6673,49 +6739,51 @@
         <v>207</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K82" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="57.6">
+    <row r="83" spans="1:11" ht="75">
       <c r="A83" s="5" t="s">
         <v>153</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="C83" s="9">
-        <v>1</v>
-      </c>
-      <c r="D83" s="10">
+        <v>275</v>
+      </c>
+      <c r="C83" s="8">
+        <v>1</v>
+      </c>
+      <c r="D83" s="20">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F83" s="5"/>
+      <c r="F83" s="5" t="s">
+        <v>214</v>
+      </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K83" s="5">
         <v>2</v>
